--- a/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC80142A-A62D-4630-B494-ABE74A1359D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65CE6C1F-BE01-4D3A-87E3-8545A3E58340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -791,10 +791,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,WaD,RaP,SaD,FaD,FaP,SaP,WaP</t>
+    <t>RaD,WaP,FaP,SaP,RaP,WaD,FaD,SaD</t>
   </si>
   <si>
-    <t>FaN,FaP,SaP,RaP,WaP,RaN,SaN,WaN</t>
+    <t>RaN,SaN,WaN,WaP,FaN,RaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24419,7 +24419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF91638-AC52-4F52-ABF7-E89436AF2117}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED91BD93-61BC-41F7-9559-C95A08DAEB8E}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24907,7 +24907,7 @@
         <v>155</v>
       </c>
       <c r="AM16">
-        <v>0.20274999999999999</v>
+        <v>0.20275000000000001</v>
       </c>
       <c r="AN16" t="s">
         <v>218</v>
@@ -25007,7 +25007,7 @@
         <v>155</v>
       </c>
       <c r="AM18">
-        <v>0.1696333333333333</v>
+        <v>0.16963333333333333</v>
       </c>
       <c r="AN18" t="s">
         <v>218</v>
@@ -25221,7 +25221,7 @@
         <v>155</v>
       </c>
       <c r="AM23">
-        <v>0.21967499999999998</v>
+        <v>0.21967500000000004</v>
       </c>
       <c r="AN23" t="s">
         <v>218</v>
@@ -25259,7 +25259,7 @@
         <v>155</v>
       </c>
       <c r="AM24">
-        <v>0.22216666666666665</v>
+        <v>0.22216666666666671</v>
       </c>
       <c r="AN24" t="s">
         <v>218</v>
@@ -25335,7 +25335,7 @@
         <v>155</v>
       </c>
       <c r="AM26">
-        <v>0.22924166666666665</v>
+        <v>0.22924166666666668</v>
       </c>
       <c r="AN26" t="s">
         <v>218</v>
@@ -25449,7 +25449,7 @@
         <v>155</v>
       </c>
       <c r="AM29">
-        <v>0.19755</v>
+        <v>0.19754999999999998</v>
       </c>
       <c r="AN29" t="s">
         <v>218</v>
@@ -25487,7 +25487,7 @@
         <v>155</v>
       </c>
       <c r="AM30">
-        <v>0.20085</v>
+        <v>0.20084999999999997</v>
       </c>
       <c r="AN30" t="s">
         <v>218</v>
@@ -25515,7 +25515,7 @@
         <v>155</v>
       </c>
       <c r="AM32">
-        <v>0.22735833333333333</v>
+        <v>0.2273583333333333</v>
       </c>
       <c r="AN32" t="s">
         <v>218</v>
@@ -25529,7 +25529,7 @@
         <v>155</v>
       </c>
       <c r="AM33">
-        <v>0.23075833333333332</v>
+        <v>0.23075833333333329</v>
       </c>
       <c r="AN33" t="s">
         <v>218</v>
@@ -25557,7 +25557,7 @@
         <v>155</v>
       </c>
       <c r="AM35">
-        <v>0.16623333333333334</v>
+        <v>0.16623333333333332</v>
       </c>
       <c r="AN35" t="s">
         <v>218</v>
@@ -25625,7 +25625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86591C29-BD5A-460A-9392-FD78398A50B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A68E995-C809-46D8-B40A-0BB4D68585B5}">
   <dimension ref="A9:AN250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25943,7 +25943,7 @@
         <v>221</v>
       </c>
       <c r="AM12">
-        <v>0.17524931119401163</v>
+        <v>0.17524931119401166</v>
       </c>
       <c r="AN12" t="s">
         <v>218</v>
@@ -26195,7 +26195,7 @@
         <v>219</v>
       </c>
       <c r="AM15">
-        <v>0.1889110593799653</v>
+        <v>0.18891105937996525</v>
       </c>
       <c r="AN15" t="s">
         <v>218</v>
@@ -26355,7 +26355,7 @@
         <v>222</v>
       </c>
       <c r="AM17">
-        <v>0.17736392861101871</v>
+        <v>0.17736392861101877</v>
       </c>
       <c r="AN17" t="s">
         <v>218</v>
@@ -26595,7 +26595,7 @@
         <v>221</v>
       </c>
       <c r="AM20">
-        <v>0.23148148148148143</v>
+        <v>0.23148148148148148</v>
       </c>
       <c r="AN20" t="s">
         <v>218</v>
@@ -26675,7 +26675,7 @@
         <v>222</v>
       </c>
       <c r="AM21">
-        <v>0.1203886572550167</v>
+        <v>0.12038865725501668</v>
       </c>
       <c r="AN21" t="s">
         <v>218</v>
@@ -26814,7 +26814,7 @@
         <v>219</v>
       </c>
       <c r="AM23">
-        <v>0.16193333333333335</v>
+        <v>0.16193333333333332</v>
       </c>
       <c r="AN23" t="s">
         <v>218</v>
@@ -26932,7 +26932,7 @@
         <v>222</v>
       </c>
       <c r="AM25">
-        <v>0.14673333333333335</v>
+        <v>0.14673333333333333</v>
       </c>
       <c r="AN25" t="s">
         <v>218</v>
@@ -27109,7 +27109,7 @@
         <v>221</v>
       </c>
       <c r="AM28">
-        <v>0.24223333333333333</v>
+        <v>0.24223333333333338</v>
       </c>
       <c r="AN28" t="s">
         <v>218</v>
@@ -27227,7 +27227,7 @@
         <v>224</v>
       </c>
       <c r="AM30">
-        <v>0.21083333333333332</v>
+        <v>0.21083333333333334</v>
       </c>
       <c r="AN30" t="s">
         <v>218</v>
@@ -27404,7 +27404,7 @@
         <v>222</v>
       </c>
       <c r="AM33">
-        <v>0.14873333333333336</v>
+        <v>0.14873333333333333</v>
       </c>
       <c r="AN33" t="s">
         <v>218</v>
@@ -27663,7 +27663,7 @@
         <v>224</v>
       </c>
       <c r="AM38">
-        <v>0.2020666666666667</v>
+        <v>0.20206666666666664</v>
       </c>
       <c r="AN38" t="s">
         <v>218</v>
@@ -28263,7 +28263,7 @@
         <v>224</v>
       </c>
       <c r="AM50">
-        <v>0.19099999999999998</v>
+        <v>0.19100000000000003</v>
       </c>
       <c r="AN50" t="s">
         <v>218</v>
@@ -28463,7 +28463,7 @@
         <v>224</v>
       </c>
       <c r="AM54">
-        <v>0.2034</v>
+        <v>0.20340000000000003</v>
       </c>
       <c r="AN54" t="s">
         <v>218</v>
@@ -28863,7 +28863,7 @@
         <v>224</v>
       </c>
       <c r="AM62">
-        <v>0.24139999999999998</v>
+        <v>0.24140000000000003</v>
       </c>
       <c r="AN62" t="s">
         <v>218</v>
@@ -28963,7 +28963,7 @@
         <v>221</v>
       </c>
       <c r="AM64">
-        <v>0.28186666666666665</v>
+        <v>0.28186666666666671</v>
       </c>
       <c r="AN64" t="s">
         <v>218</v>
@@ -29163,7 +29163,7 @@
         <v>221</v>
       </c>
       <c r="AM68">
-        <v>0.30520000000000003</v>
+        <v>0.30519999999999997</v>
       </c>
       <c r="AN68" t="s">
         <v>218</v>
@@ -29863,7 +29863,7 @@
         <v>224</v>
       </c>
       <c r="AM82">
-        <v>0.23576666666666668</v>
+        <v>0.23576666666666665</v>
       </c>
       <c r="AN82" t="s">
         <v>218</v>
@@ -29913,7 +29913,7 @@
         <v>219</v>
       </c>
       <c r="AM83">
-        <v>0.17123333333333335</v>
+        <v>0.17123333333333332</v>
       </c>
       <c r="AN83" t="s">
         <v>218</v>
@@ -30113,7 +30113,7 @@
         <v>219</v>
       </c>
       <c r="AM87">
-        <v>0.16470000000000001</v>
+        <v>0.16469999999999999</v>
       </c>
       <c r="AN87" t="s">
         <v>218</v>
@@ -30163,7 +30163,7 @@
         <v>221</v>
       </c>
       <c r="AM88">
-        <v>0.2588333333333333</v>
+        <v>0.25883333333333336</v>
       </c>
       <c r="AN88" t="s">
         <v>218</v>
@@ -30863,7 +30863,7 @@
         <v>224</v>
       </c>
       <c r="AM102">
-        <v>0.26203333333333328</v>
+        <v>0.26203333333333334</v>
       </c>
       <c r="AN102" t="s">
         <v>218</v>
@@ -31263,7 +31263,7 @@
         <v>224</v>
       </c>
       <c r="AM110">
-        <v>0.19033333333333335</v>
+        <v>0.19033333333333333</v>
       </c>
       <c r="AN110" t="s">
         <v>218</v>
@@ -31813,7 +31813,7 @@
         <v>222</v>
       </c>
       <c r="AM121">
-        <v>0.15029999999999999</v>
+        <v>0.15030000000000002</v>
       </c>
       <c r="AN121" t="s">
         <v>218</v>
@@ -32013,7 +32013,7 @@
         <v>222</v>
       </c>
       <c r="AM125">
-        <v>0.13863333333333336</v>
+        <v>0.13863333333333333</v>
       </c>
       <c r="AN125" t="s">
         <v>218</v>
@@ -32063,7 +32063,7 @@
         <v>224</v>
       </c>
       <c r="AM126">
-        <v>0.22689999999999999</v>
+        <v>0.22690000000000002</v>
       </c>
       <c r="AN126" t="s">
         <v>218</v>
